--- a/outputs/figure_source_data/source_data_fig_4_e.xlsx
+++ b/outputs/figure_source_data/source_data_fig_4_e.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Wilson 95% confidence interval.</t>
+          <t>Wilson 90% confidence interval for 48 student pair-level judgments.</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -644,14 +644,14 @@
         <v>0.5208333333333334</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.383292323033428</v>
+        <v>0.404319965986563</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.6552868382304839</v>
+        <v>0.6351234530906951</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Wilson 95% CI</t>
+          <t>Wilson 90% CI</t>
         </is>
       </c>
     </row>
